--- a/Output/PowerPoint_Figures/Fig_8/Axisless/Axis_Scaling_Reference.xlsx
+++ b/Output/PowerPoint_Figures/Fig_8/Axisless/Axis_Scaling_Reference.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig_8_Axis_Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fig_8_Axis_Info" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,154 +413,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="5" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>X_Label</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Y_Label</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>X_Scale</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Y_Scale</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>X_Min</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>X_Max</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Y_Min</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Y_Max</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>X_Ticks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>X_Tick_Step</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>Y_Ticks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Y_Tick_Step</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Colorbar_Min</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Colorbar_White</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Colorbar_Max</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Colorbar_Label</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Colorbar_Tick_Step</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Original_Width_in</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Original_Height_in</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Axisless_Width_in</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Axisless_Height_in</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Axisless_Width_px</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Axisless_Height_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>DPI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Colorbar_Min</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Colorbar_Max</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Colorbar_Label</t>
         </is>
       </c>
     </row>
@@ -584,80 +566,87 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fig_8a.png</t>
+          <t>Fig_8b.png</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>False Positive Rate</t>
+          <t>Predicted</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>True Positive Rate</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0, 0.2, 0.4, 0.6, 0.8, 1.0</t>
+          <t>Neg, Pos</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0, 0.2, 0.4, 0.6, 0.8, 1.0</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1690</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1548</v>
-      </c>
-      <c r="T2" t="n">
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Neg, Pos</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA2" t="n">
         <v>600</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Concern (Binary) ROC curve with std shading, chance line at diagonal</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Concern (Binary) confusion matrix (counts only), Blues cmap. 2x2 cells: TN/FP/FN/TP.</t>
         </is>
       </c>
     </row>
@@ -669,12 +658,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>b (with %)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fig_8b.png</t>
+          <t>Fig_8b_with_pct.png</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -697,26 +686,10 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Neg, Pos</t>
@@ -724,33 +697,48 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Neg, Pos</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R3" t="n">
-        <v>803</v>
-      </c>
-      <c r="S3" t="n">
-        <v>803</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>10</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA3" t="n">
         <v>600</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Concern (Binary) confusion matrix, Blues cmap, counts only</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Concern (Binary) confusion matrix with row percentages (e.g. "73 (66.4%)")</t>
         </is>
       </c>
     </row>
@@ -762,22 +750,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b (with %)</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fig_8b_with_pct.png</t>
+          <t>Fig_8c.png</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Predicted</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -787,63 +775,64 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.15</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Neg, Pos</t>
+          <t>Accuracy, AUC ROC, F1, MCC</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Neg, Pos</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1.66</v>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.0, 0.2, 0.4, 0.6, 0.8, 1.0</t>
+        </is>
       </c>
       <c r="O4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R4" t="n">
-        <v>743</v>
-      </c>
-      <c r="S4" t="n">
-        <v>743</v>
-      </c>
-      <c r="T4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA4" t="n">
         <v>600</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Concern (Binary) confusion matrix with row percentages</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Concern (Binary) 4-metric bar chart with error bars (mean +/- std across folds)</t>
         </is>
       </c>
     </row>
@@ -855,84 +844,97 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fig_8c.png</t>
+          <t>Fig_8d.png</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Prob (%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Drug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.15</v>
+          <t>categorical (25 drugs, sorted by prob)</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>105</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>(row 0)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>(row 24)</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Acc, AUC ROC, F1, MCC</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R5" t="n">
-        <v>666</v>
-      </c>
-      <c r="S5" t="n">
-        <v>616</v>
-      </c>
-      <c r="T5" t="n">
+          <t>0, 20, 40, 60, 80, 100</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Amiodarone, Bortezomib, Chlorpromazine, Cobimetinib, Dactinomycin, Daunorubicin, Doxorubicin, Epirubicin, Erlotinib, Etomoxir, Gemcitibine, Ibrutinib, Ibuprofen, Isoproterenol, Mexiletine, Nifedipine, Panobinostat, Plicamycin, Rosiglitazone, Sotalol, Sunitinib, Vandetanib, Vincristine, Vioxx, Vorinostat</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA5" t="n">
         <v>600</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Concern (Binary) performance bar chart with error bars, 4 metrics</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Concern (Binary) per-drug prob scatter. Green=positive, red=negative. Threshold line at 35%%.</t>
         </is>
       </c>
     </row>
@@ -944,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>d (with stats)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fig_8d.png</t>
+          <t>Fig_8d_with_stats.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -969,7 +971,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>categorical (drug names)</t>
+          <t>categorical (25 drugs)</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -980,48 +982,61 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(row 0)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(row 24)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>drug names</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R6" t="n">
-        <v>705</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1096</v>
-      </c>
-      <c r="T6" t="n">
+          <t>0, 20, 40, 60, 80, 100</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>20</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Amiodarone, Bortezomib, Chlorpromazine, Cobimetinib, Dactinomycin, Daunorubicin, Doxorubicin, Epirubicin, Erlotinib, Etomoxir, Gemcitibine, Ibrutinib, Ibuprofen, Isoproterenol, Mexiletine, Nifedipine, Panobinostat, Plicamycin, Rosiglitazone, Sotalol, Sunitinib, Vandetanib, Vincristine, Vioxx, Vorinostat</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>10</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>10</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA6" t="n">
         <v>600</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Concern (Binary) threshold analysis, scatter + vertical threshold line, green=positive red=negative</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Concern (Binary) threshold plot with mean +/- std bands per class (positive/negative)</t>
         </is>
       </c>
     </row>
@@ -1033,84 +1048,91 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d (with stats)</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fig_8d_with_stats.png</t>
+          <t>Fig_8e.png</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prob (%)</t>
+          <t># Features</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drug</t>
+          <t>Cumulative Score (%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>linear (integer)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>categorical (drug names)</t>
-        </is>
-      </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
         <v>-5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>105</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>drug names</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1.59</v>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0, 20, 40, 60, 80, 100</t>
+        </is>
       </c>
       <c r="O7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R7" t="n">
-        <v>645</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1036</v>
-      </c>
-      <c r="T7" t="n">
+        <v>20</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA7" t="n">
         <v>600</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Concern (Binary) threshold with mean +/- std bands per class</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Concern (Binary) cumulative feature importance. One line per drug (25 lines). Horizontal threshold line at 35%.</t>
         </is>
       </c>
     </row>
@@ -1122,161 +1144,95 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fig_8e.png</t>
+          <t>Fig_8f.png</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t># Features</t>
+          <t>SHAP Value (impact on model output)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cumulative Score (%)</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>linear (integer)</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>categorical (14 features)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>-0.648</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>105</v>
+        <v>0.146</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>(row 0)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>(row 13)</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1, 2, ..., 14</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1098</v>
-      </c>
-      <c r="S8" t="n">
-        <v>899</v>
-      </c>
-      <c r="T8" t="n">
+          <t>matplotlib auto (symmetric around 0)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>R0_Contractility, Emax_Contractility, kappa_Contractility, n_Contractility, m_Contractility, tau_Contractility, k_elim_Contractility, R0_O2, Emax_O2, kappa_O2, n_O2, m_O2, tau_O2, k_elim_O2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>categorical (non-uniform bins)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AA8" t="n">
         <v>600</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Concern (Binary) cumulative feature importance, per-drug lines, threshold line</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Fig_8f.png</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SHAP Value (impact on model output)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>14 coefficient features</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="T9" t="n">
-        <v>600</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Concern (Binary) SHAP aligned pairs (from shap_aligned_pairs_all.py)</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Concern (Binary) SHAP aligned pairs. Drugs sorted by |SHAP| descending. Positive extends right, negative extends left.</t>
         </is>
       </c>
     </row>
